--- a/InputData/elec/BPHC/BAU Pumped Hydro Cap.xlsx
+++ b/InputData/elec/BPHC/BAU Pumped Hydro Cap.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iamho\Dropbox\Energy Innovation\InputData_Working\홍상현\elec\BPHC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\2026\01.EPS\01.EI\01.메일_업무협의\260908_메일회신\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D887309D-9233-43F4-9FAE-4961B7DB4E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8BB84E4F-B2B9-4D1C-B011-A2F96D59C4E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1970" yWindow="0" windowWidth="28830" windowHeight="18770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="KPX" sheetId="5" r:id="rId2"/>
-    <sheet name="BPHC" sheetId="3" r:id="rId3"/>
+    <sheet name="제11차 전기본" sheetId="6" r:id="rId3"/>
+    <sheet name="BPHC" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="gigawatts_to_megawatts">About!$B$9</definedName>
+    <definedName name="gigawatts_to_megawatts">About!$B$15</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,8 +35,42 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>administer</author>
+  </authors>
+  <commentList>
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{5C96CF51-D6B0-4343-95A0-1597B1CC1B67}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>administer:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Source: 제11차 전력수급기본계획 (uploaded image), p.93, 전원구성 전망 표</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
   <si>
     <t>BPHC BAU Pumped Hydro Capacity</t>
   </si>
@@ -47,9 +82,6 @@
   </si>
   <si>
     <t>Pumped Storage Capacity (MW)</t>
-  </si>
-  <si>
-    <t>Capacities by Plant Type</t>
   </si>
   <si>
     <t>KPX</t>
@@ -124,15 +156,41 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>We assumed the current level of PHS capacity will be maintailed</t>
+    <t>전원구성 전망 - 양수 (단위: GW)</t>
+  </si>
+  <si>
+    <t>구분</t>
+  </si>
+  <si>
+    <t>양수(GW)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reflects the pumped-storage hydro capacity plan from the 11th Basic Plan for Electricity Supply and Demand (Ministry of Trade, Industry and Energy, 2025). </t>
     <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assumes KPX EPSIS actual levels are maintained for 2020-2029, the 11th Plan figures for 2030-2038, and the plan's endpoint (10,400 MW) held constant for 2039-2050.</t>
+  </si>
+  <si>
+    <t>Capacities by Plant Type(2019~2023)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Capacities by Plant Type(2024~2038)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>11th Basic Plan for Electricity Supply and Demand</t>
+  </si>
+  <si>
+    <t>Ministry of Trade, Industry and Energy</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -183,8 +241,29 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -194,6 +273,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -264,12 +349,11 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -278,6 +362,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Body: normal cell" xfId="6" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -303,10 +390,151 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>610251</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>105134</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13A8D7D3-20F5-E45B-D2E4-359B4BDA3A0B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4857750" y="895350"/>
+          <a:ext cx="4667901" cy="2572109"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>10178</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>172389</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="그림 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{76027C89-2B7E-FD12-D398-AB99D20A823C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4933950" y="3724275"/>
+          <a:ext cx="4677428" cy="6725589"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>646</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>58105</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="그림 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F147E7B-9DF6-93E9-0446-384E75F64E74}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="171450" y="981075"/>
+          <a:ext cx="4629796" cy="6839905"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -344,9 +572,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -379,26 +607,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -431,26 +642,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -622,69 +816,121 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="7">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{30B49787-82BD-46E6-8860-F44FCCB29A64}">
+  <we:reference id="11d7cf85-ae5a-43b8-bc58-1e1a151cce24" version="1.0.0.1" store="EXCatalog" storeType="EXCatalog"/>
+  <we:alternateReferences>
+    <we:reference id="WA200010725" version="1.0.0.1" store="ko-KR" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;dc142ee2-fe6d-4da0-9ebd-23ce6feeb0f8&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B5" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A5" s="4"/>
-      <c r="B5" s="6" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4" t="s">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A7" s="4"/>
-      <c r="B7" s="2" t="s">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B8" s="2"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B9" s="2"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B10" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B11" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B12" s="5">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B13" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A9" s="1" t="s">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="4"/>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A10" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="4">
+      <c r="B16">
         <v>2019</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>26</v>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -700,535 +946,535 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D246FC7-B2DD-445B-851D-44E988A708A4}">
   <dimension ref="A1:Q10"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K1" s="4" t="s">
+      <c r="M1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="M1" s="7" t="s">
+      <c r="N1" t="s">
         <v>20</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" t="s">
         <v>21</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" t="s">
         <v>22</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="Q1" t="s">
         <v>23</v>
       </c>
-      <c r="Q1" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A2" s="4">
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A2">
         <v>2020</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="7">
         <v>23250</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="7">
         <v>36453.379999999997</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2">
         <v>400</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="7">
         <v>2247.0300000000002</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2" s="7">
         <v>41169.769999999997</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G2" s="7">
         <v>4700</v>
       </c>
-      <c r="H2" s="4">
+      <c r="H2">
         <v>604.71</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2">
         <v>346.33</v>
       </c>
-      <c r="J2" s="8">
+      <c r="J2" s="7">
         <v>14574.79</v>
       </c>
-      <c r="K2" s="8">
+      <c r="K2" s="7">
         <v>1635.8</v>
       </c>
-      <c r="L2" s="8">
+      <c r="L2" s="7">
         <v>1805.77</v>
       </c>
-      <c r="M2" s="4">
+      <c r="M2">
         <v>255.5</v>
       </c>
-      <c r="N2" s="8">
+      <c r="N2" s="7">
         <v>1321.99</v>
       </c>
-      <c r="O2" s="4">
+      <c r="O2">
         <v>0</v>
       </c>
-      <c r="P2" s="4">
+      <c r="P2">
         <v>426.2</v>
       </c>
-      <c r="Q2" s="8">
+      <c r="Q2" s="7">
         <v>129191.27</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A3" s="4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A3">
         <v>2019</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="7">
         <v>23250</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="7">
         <v>36391.78</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3">
         <v>600</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="7">
         <v>3771.04</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="7">
         <v>39655.4</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="7">
         <v>4700</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3">
         <v>464.15</v>
       </c>
-      <c r="I3" s="4">
+      <c r="I3">
         <v>346.33</v>
       </c>
-      <c r="J3" s="8">
+      <c r="J3" s="7">
         <v>10505.1</v>
       </c>
-      <c r="K3" s="8">
+      <c r="K3" s="7">
         <v>1512.22</v>
       </c>
-      <c r="L3" s="8">
+      <c r="L3" s="7">
         <v>1808.1</v>
       </c>
-      <c r="M3" s="4">
+      <c r="M3">
         <v>255.5</v>
       </c>
-      <c r="N3" s="4">
+      <c r="N3">
         <v>899.65</v>
       </c>
-      <c r="O3" s="4">
+      <c r="O3">
         <v>0</v>
       </c>
-      <c r="P3" s="8">
+      <c r="P3" s="7">
         <v>1178.3900000000001</v>
       </c>
-      <c r="Q3" s="8">
+      <c r="Q3" s="7">
         <v>125337.67</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A4" s="4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A4">
         <v>2018</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="7">
         <v>21850</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="7">
         <v>36298.74</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4">
         <v>600</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="7">
         <v>4318.62</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="7">
         <v>37834.39</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="7">
         <v>4700</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4">
         <v>343.69</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4">
         <v>346.33</v>
       </c>
-      <c r="J4" s="8">
+      <c r="J4" s="7">
         <v>7129.86</v>
       </c>
-      <c r="K4" s="8">
+      <c r="K4" s="7">
         <v>1420.33</v>
       </c>
-      <c r="L4" s="8">
+      <c r="L4" s="7">
         <v>1790.41</v>
       </c>
-      <c r="M4" s="4">
+      <c r="M4">
         <v>255</v>
       </c>
-      <c r="N4" s="4">
+      <c r="N4">
         <v>537.66</v>
       </c>
-      <c r="O4" s="8">
+      <c r="O4" s="7">
         <v>1589.94</v>
       </c>
-      <c r="P4" s="4">
+      <c r="P4">
         <v>76.7</v>
       </c>
-      <c r="Q4" s="8">
+      <c r="Q4" s="7">
         <v>119091.66</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A5" s="4">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A5">
         <v>2017</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="7">
         <v>22528.68</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="7">
         <v>36097.800000000003</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5">
         <v>600</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="7">
         <v>4150.57</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="7">
         <v>37832.699999999997</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="7">
         <v>4700</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5">
         <v>246.9</v>
       </c>
-      <c r="I5" s="4">
+      <c r="I5">
         <v>346.33</v>
       </c>
-      <c r="J5" s="8">
+      <c r="J5" s="7">
         <v>5062.3100000000004</v>
       </c>
-      <c r="K5" s="8">
+      <c r="K5" s="7">
         <v>1214.82</v>
       </c>
-      <c r="L5" s="8">
+      <c r="L5" s="7">
         <v>1789.46</v>
       </c>
-      <c r="M5" s="4">
+      <c r="M5">
         <v>255.11</v>
       </c>
-      <c r="N5" s="4">
+      <c r="N5">
         <v>494.42</v>
       </c>
-      <c r="O5" s="8">
+      <c r="O5" s="7">
         <v>1567.03</v>
       </c>
-      <c r="P5" s="4">
+      <c r="P5">
         <v>21.51</v>
       </c>
-      <c r="Q5" s="8">
+      <c r="Q5" s="7">
         <v>116907.64</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A6" s="4">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A6">
         <v>2016</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="7">
         <v>23115.68</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="7">
         <v>30898.42</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="7">
         <v>1125</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="7">
         <v>4140.54</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="7">
         <v>32602.1</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="7">
         <v>4700</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6">
         <v>214.82</v>
       </c>
-      <c r="I6" s="4">
+      <c r="I6">
         <v>346.33</v>
       </c>
-      <c r="J6" s="8">
+      <c r="J6" s="7">
         <v>3716.32</v>
       </c>
-      <c r="K6" s="8">
+      <c r="K6" s="7">
         <v>1051.01</v>
       </c>
-      <c r="L6" s="8">
+      <c r="L6" s="7">
         <v>1785.21</v>
       </c>
-      <c r="M6" s="4">
+      <c r="M6">
         <v>255.11</v>
       </c>
-      <c r="N6" s="4">
+      <c r="N6">
         <v>353.26</v>
       </c>
-      <c r="O6" s="8">
+      <c r="O6" s="7">
         <v>1561.76</v>
       </c>
-      <c r="P6" s="4">
+      <c r="P6">
         <v>0</v>
       </c>
-      <c r="Q6" s="8">
+      <c r="Q6" s="7">
         <v>105865.56</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A7" s="4">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A7">
         <v>2015</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="7">
         <v>21715.68</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="7">
         <v>26201.91</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="7">
         <v>1125</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="7">
         <v>4242.59</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="7">
         <v>32243.5</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="7">
         <v>4700</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H7">
         <v>171.4</v>
       </c>
-      <c r="I7" s="4">
+      <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7" s="8">
+      <c r="J7" s="7">
         <v>2537.56</v>
       </c>
-      <c r="K7" s="4">
+      <c r="K7">
         <v>834.42</v>
       </c>
-      <c r="L7" s="8">
+      <c r="L7" s="7">
         <v>1770.71</v>
       </c>
-      <c r="M7" s="4">
+      <c r="M7">
         <v>255</v>
       </c>
-      <c r="N7" s="4">
+      <c r="N7">
         <v>244.89</v>
       </c>
-      <c r="O7" s="8">
+      <c r="O7" s="7">
         <v>1606.1</v>
       </c>
-      <c r="P7" s="4">
+      <c r="P7">
         <v>0</v>
       </c>
-      <c r="Q7" s="8">
+      <c r="Q7" s="7">
         <v>97648.76</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A8" s="4">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A8">
         <v>2014</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="7">
         <v>20715.68</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="7">
         <v>25910.51</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="7">
         <v>1125</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="7">
         <v>4254.99</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="7">
         <v>30268.69</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="7">
         <v>4700</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8">
         <v>161.4</v>
       </c>
-      <c r="I8" s="4">
+      <c r="I8">
         <v>0</v>
       </c>
-      <c r="J8" s="8">
+      <c r="J8" s="7">
         <v>1791.18</v>
       </c>
-      <c r="K8" s="4">
+      <c r="K8">
         <v>603.97</v>
       </c>
-      <c r="L8" s="8">
+      <c r="L8" s="7">
         <v>1766.94</v>
       </c>
-      <c r="M8" s="4">
+      <c r="M8">
         <v>255</v>
       </c>
-      <c r="N8" s="4">
+      <c r="N8">
         <v>137.47999999999999</v>
       </c>
-      <c r="O8" s="8">
+      <c r="O8" s="7">
         <v>1524.91</v>
       </c>
-      <c r="P8" s="4">
+      <c r="P8">
         <v>0</v>
       </c>
-      <c r="Q8" s="8">
+      <c r="Q8" s="7">
         <v>93215.75</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A9" s="4">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A9">
         <v>2013</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="7">
         <v>20715.68</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="7">
         <v>24110.51</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="7">
         <v>1125</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="7">
         <v>5254.99</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="7">
         <v>25789.59</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="7">
         <v>4700</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H9">
         <v>126.66</v>
       </c>
-      <c r="I9" s="4">
+      <c r="I9">
         <v>0</v>
       </c>
-      <c r="J9" s="8">
+      <c r="J9" s="7">
         <v>1079.8499999999999</v>
       </c>
-      <c r="K9" s="4">
+      <c r="K9">
         <v>554.59</v>
       </c>
-      <c r="L9" s="8">
+      <c r="L9" s="7">
         <v>1754.46</v>
       </c>
-      <c r="M9" s="4">
+      <c r="M9">
         <v>255</v>
       </c>
-      <c r="N9" s="4">
+      <c r="N9">
         <v>126.68</v>
       </c>
-      <c r="O9" s="8">
+      <c r="O9" s="7">
         <v>1375.92</v>
       </c>
-      <c r="P9" s="4">
+      <c r="P9">
         <v>0</v>
       </c>
-      <c r="Q9" s="8">
+      <c r="Q9" s="7">
         <v>86968.94</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A10" s="4">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A10">
         <v>2012</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="7">
         <v>20715.68</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="7">
         <v>24003.11</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="7">
         <v>1125</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="7">
         <v>5292.64</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="7">
         <v>21885.06</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="7">
         <v>4700</v>
       </c>
-      <c r="H10" s="4">
+      <c r="H10">
         <v>56.1</v>
       </c>
-      <c r="I10" s="4">
+      <c r="I10">
         <v>0</v>
       </c>
-      <c r="J10" s="4">
+      <c r="J10">
         <v>690.27</v>
       </c>
-      <c r="K10" s="4">
+      <c r="K10">
         <v>476.74</v>
       </c>
-      <c r="L10" s="8">
+      <c r="L10" s="7">
         <v>1746.03</v>
       </c>
-      <c r="M10" s="4">
+      <c r="M10">
         <v>255</v>
       </c>
-      <c r="N10" s="4">
+      <c r="N10">
         <v>93.37</v>
       </c>
-      <c r="O10" s="4">
+      <c r="O10">
         <v>766.57</v>
       </c>
-      <c r="P10" s="4">
+      <c r="P10">
         <v>0</v>
       </c>
-      <c r="Q10" s="8">
+      <c r="Q10" s="7">
         <v>81805.58</v>
       </c>
     </row>
@@ -1239,17 +1485,141 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4096E87-C434-4D7B-9768-DD3FDE42A7AE}">
+  <dimension ref="A1:Q4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:17" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A3" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="9">
+        <v>2023</v>
+      </c>
+      <c r="C3" s="9">
+        <v>2024</v>
+      </c>
+      <c r="D3" s="9">
+        <v>2025</v>
+      </c>
+      <c r="E3" s="9">
+        <v>2026</v>
+      </c>
+      <c r="F3" s="9">
+        <v>2027</v>
+      </c>
+      <c r="G3" s="9">
+        <v>2028</v>
+      </c>
+      <c r="H3" s="9">
+        <v>2029</v>
+      </c>
+      <c r="I3" s="9">
+        <v>2030</v>
+      </c>
+      <c r="J3" s="9">
+        <v>2031</v>
+      </c>
+      <c r="K3" s="9">
+        <v>2032</v>
+      </c>
+      <c r="L3" s="9">
+        <v>2033</v>
+      </c>
+      <c r="M3" s="9">
+        <v>2034</v>
+      </c>
+      <c r="N3" s="9">
+        <v>2035</v>
+      </c>
+      <c r="O3" s="9">
+        <v>2036</v>
+      </c>
+      <c r="P3" s="9">
+        <v>2037</v>
+      </c>
+      <c r="Q3" s="9">
+        <v>2038</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4">
+        <v>4.7</v>
+      </c>
+      <c r="C4">
+        <v>4.7</v>
+      </c>
+      <c r="D4">
+        <v>4.7</v>
+      </c>
+      <c r="E4">
+        <v>4.7</v>
+      </c>
+      <c r="F4">
+        <v>4.7</v>
+      </c>
+      <c r="G4">
+        <v>4.7</v>
+      </c>
+      <c r="H4">
+        <v>4.7</v>
+      </c>
+      <c r="I4">
+        <v>5.2</v>
+      </c>
+      <c r="J4">
+        <v>5.2</v>
+      </c>
+      <c r="K4">
+        <v>5.8</v>
+      </c>
+      <c r="L4">
+        <v>6.5</v>
+      </c>
+      <c r="M4">
+        <v>7.9</v>
+      </c>
+      <c r="N4">
+        <v>7.9</v>
+      </c>
+      <c r="O4">
+        <v>9.4</v>
+      </c>
+      <c r="P4">
+        <v>10.4</v>
+      </c>
+      <c r="Q4">
+        <v>10.4</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AG2"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.4140625" customWidth="1"/>
+    <col min="1" max="1" width="30.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1347,7 +1717,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1364,116 +1734,116 @@
         <v>4700</v>
       </c>
       <c r="E2" s="3">
-        <f t="shared" si="0"/>
+        <f>'제11차 전기본'!B4*1000</f>
         <v>4700</v>
       </c>
       <c r="F2" s="3">
-        <f t="shared" si="0"/>
+        <f>'제11차 전기본'!C4*1000</f>
         <v>4700</v>
       </c>
       <c r="G2" s="3">
-        <f t="shared" si="0"/>
+        <f>'제11차 전기본'!D4*1000</f>
         <v>4700</v>
       </c>
       <c r="H2" s="3">
-        <f t="shared" si="0"/>
+        <f>'제11차 전기본'!E4*1000</f>
         <v>4700</v>
       </c>
       <c r="I2" s="3">
-        <f t="shared" si="0"/>
+        <f>'제11차 전기본'!F4*1000</f>
         <v>4700</v>
       </c>
       <c r="J2" s="3">
-        <f t="shared" si="0"/>
+        <f>'제11차 전기본'!G4*1000</f>
         <v>4700</v>
       </c>
       <c r="K2" s="3">
-        <f t="shared" si="0"/>
+        <f>'제11차 전기본'!H4*1000</f>
         <v>4700</v>
       </c>
       <c r="L2" s="3">
-        <f t="shared" si="0"/>
-        <v>4700</v>
+        <f>'제11차 전기본'!I4*1000</f>
+        <v>5200</v>
       </c>
       <c r="M2" s="3">
-        <f t="shared" si="0"/>
-        <v>4700</v>
+        <f>'제11차 전기본'!J4*1000</f>
+        <v>5200</v>
       </c>
       <c r="N2" s="3">
-        <f t="shared" si="0"/>
-        <v>4700</v>
+        <f>'제11차 전기본'!K4*1000</f>
+        <v>5800</v>
       </c>
       <c r="O2" s="3">
-        <f t="shared" si="0"/>
-        <v>4700</v>
+        <f>'제11차 전기본'!L4*1000</f>
+        <v>6500</v>
       </c>
       <c r="P2" s="3">
-        <f t="shared" si="0"/>
-        <v>4700</v>
+        <f>'제11차 전기본'!M4*1000</f>
+        <v>7900</v>
       </c>
       <c r="Q2" s="3">
-        <f t="shared" si="0"/>
-        <v>4700</v>
+        <f>'제11차 전기본'!N4*1000</f>
+        <v>7900</v>
       </c>
       <c r="R2" s="3">
-        <f t="shared" si="0"/>
-        <v>4700</v>
+        <f>'제11차 전기본'!O4*1000</f>
+        <v>9400</v>
       </c>
       <c r="S2" s="3">
-        <f t="shared" si="0"/>
-        <v>4700</v>
+        <f>'제11차 전기본'!P4*1000</f>
+        <v>10400</v>
       </c>
       <c r="T2" s="3">
-        <f t="shared" si="0"/>
-        <v>4700</v>
+        <f>'제11차 전기본'!Q4*1000</f>
+        <v>10400</v>
       </c>
       <c r="U2" s="3">
         <f t="shared" si="0"/>
-        <v>4700</v>
+        <v>10400</v>
       </c>
       <c r="V2" s="3">
         <f t="shared" si="0"/>
-        <v>4700</v>
+        <v>10400</v>
       </c>
       <c r="W2" s="3">
         <f t="shared" si="0"/>
-        <v>4700</v>
+        <v>10400</v>
       </c>
       <c r="X2" s="3">
         <f t="shared" si="0"/>
-        <v>4700</v>
+        <v>10400</v>
       </c>
       <c r="Y2" s="3">
         <f t="shared" si="0"/>
-        <v>4700</v>
+        <v>10400</v>
       </c>
       <c r="Z2" s="3">
         <f t="shared" si="0"/>
-        <v>4700</v>
+        <v>10400</v>
       </c>
       <c r="AA2" s="3">
         <f t="shared" si="0"/>
-        <v>4700</v>
+        <v>10400</v>
       </c>
       <c r="AB2" s="3">
         <f t="shared" si="0"/>
-        <v>4700</v>
+        <v>10400</v>
       </c>
       <c r="AC2" s="3">
         <f t="shared" si="0"/>
-        <v>4700</v>
+        <v>10400</v>
       </c>
       <c r="AD2" s="3">
         <f t="shared" si="0"/>
-        <v>4700</v>
+        <v>10400</v>
       </c>
       <c r="AE2" s="3">
         <f t="shared" si="0"/>
-        <v>4700</v>
+        <v>10400</v>
       </c>
       <c r="AF2" s="3">
         <f t="shared" si="0"/>
-        <v>4700</v>
+        <v>10400</v>
       </c>
       <c r="AG2" s="3"/>
     </row>
@@ -1484,6 +1854,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
     <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
@@ -1627,29 +2012,37 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8354EBE5-CDA7-4D5D-83D8-D6C62EA6D048}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F858930-8C7A-4C63-B641-38E4DF088097}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C610B1EF-C37C-4C4A-AC5E-85E9938BD89A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C610B1EF-C37C-4C4A-AC5E-85E9938BD89A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F858930-8C7A-4C63-B641-38E4DF088097}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8354EBE5-CDA7-4D5D-83D8-D6C62EA6D048}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>